--- a/Result/checksun/居家生活.xlsx
+++ b/Result/checksun/居家生活.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32733,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33021,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33309,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33597,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33885,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34173,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34461,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -34749,7 +35177,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35037,7 +35469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35325,7 +35761,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -35905,7 +36345,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36193,7 +36637,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36481,7 +36929,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -36769,7 +37221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37057,7 +37513,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37345,7 +37805,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37633,7 +38097,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -37921,7 +38389,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38209,7 +38681,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38497,7 +38973,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -39077,7 +39557,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -39365,7 +39849,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -39653,7 +40141,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -39941,7 +40433,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -40229,7 +40725,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -40517,7 +41017,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -40805,7 +41309,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -41093,7 +41601,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -41381,7 +41893,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -41669,7 +42185,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -42249,7 +42769,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -42537,7 +43061,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -42825,7 +43353,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -43113,7 +43645,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -43401,7 +43937,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -43689,7 +44229,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -43977,7 +44521,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -44265,7 +44813,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -44553,7 +45105,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -44841,7 +45397,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -45421,7 +45981,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -45709,7 +46273,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -45997,7 +46565,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -46285,7 +46857,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -46573,7 +47149,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -46861,7 +47441,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -47149,7 +47733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -47437,7 +48025,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -47725,7 +48317,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -48013,7 +48609,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -48593,7 +49193,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -48881,7 +49485,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -49169,7 +49777,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -49457,7 +50069,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -49745,7 +50361,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr"/>
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -50033,7 +50653,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -50321,7 +50945,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -50609,7 +51237,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -50897,7 +51529,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -51185,7 +51821,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -51765,7 +52405,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -52053,7 +52697,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -52341,7 +52989,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -52629,7 +53281,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -52917,7 +53573,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr"/>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -53205,7 +53865,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -53493,7 +54157,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -53781,7 +54449,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -54069,7 +54741,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -54357,7 +55033,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -54937,7 +55617,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -55225,7 +55909,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -55513,7 +56201,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -55801,7 +56493,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -56089,7 +56785,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr"/>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -56377,7 +57077,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -56665,7 +57369,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -56953,7 +57661,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -57241,7 +57953,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -57529,7 +58245,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -58109,7 +58829,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -58397,7 +59121,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -58685,7 +59413,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -58973,7 +59705,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -59261,7 +59997,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr"/>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -59549,7 +60289,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -59837,7 +60581,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -60125,7 +60873,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -60413,7 +61165,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -60701,7 +61457,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -61281,7 +62041,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -61569,7 +62333,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -61857,7 +62625,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -62145,7 +62917,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -62433,7 +63209,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr"/>
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -62721,7 +63501,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -63009,7 +63793,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -63297,7 +64085,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -63585,7 +64377,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -63873,7 +64669,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -64453,7 +65253,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -64741,7 +65545,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -65029,7 +65837,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -65317,7 +66129,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -65605,7 +66421,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -65893,7 +66713,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -66181,7 +67005,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -66469,7 +67297,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -66757,7 +67589,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -67045,7 +67881,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -67625,7 +68465,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -67913,7 +68757,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -68201,7 +69049,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -68489,7 +69341,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -68777,7 +69633,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -69065,7 +69925,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -69353,7 +70217,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -69641,7 +70509,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -69929,7 +70801,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -70217,7 +71093,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr"/>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -70797,7 +71677,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr"/>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -71085,7 +71969,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr"/>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -71373,7 +72261,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -71661,7 +72553,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -71949,7 +72845,11 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr"/>
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -72237,7 +73137,11 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr"/>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -72525,7 +73429,11 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -72813,7 +73721,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -73101,7 +74013,11 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -73389,7 +74305,11 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -73969,7 +74889,11 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -74257,7 +75181,11 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -74545,7 +75473,11 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr"/>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -74833,7 +75765,11 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr"/>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -75121,7 +76057,11 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr"/>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -75409,7 +76349,11 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr"/>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -75697,7 +76641,11 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -75985,7 +76933,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -76273,7 +77225,11 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -76561,7 +77517,11 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -77141,7 +78101,11 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr"/>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -77429,7 +78393,11 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -77717,7 +78685,11 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr"/>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -78005,7 +78977,11 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr"/>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -78293,7 +79269,11 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr"/>
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -78581,7 +79561,11 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr"/>
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -78869,7 +79853,11 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr"/>
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -79157,7 +80145,11 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr"/>
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -79445,7 +80437,11 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr"/>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -79733,7 +80729,11 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr"/>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -80313,7 +81313,11 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr"/>
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -80601,7 +81605,11 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr"/>
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -80889,7 +81897,11 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr"/>
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -81177,7 +82189,11 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr"/>
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -81465,7 +82481,11 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr"/>
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -81753,7 +82773,11 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr"/>
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -82041,7 +83065,11 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr"/>
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -82329,7 +83357,11 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr"/>
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -82617,7 +83649,11 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr"/>
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -82905,7 +83941,11 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr"/>
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -83485,7 +84525,11 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr"/>
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -83773,7 +84817,11 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr"/>
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -84061,7 +85109,11 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr"/>
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -84349,7 +85401,11 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr"/>
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -84637,7 +85693,11 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr"/>
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -84925,7 +85985,11 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr"/>
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -85213,7 +86277,11 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr"/>
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -85501,7 +86569,11 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -85789,7 +86861,11 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr"/>
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -86077,7 +87153,11 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -86657,7 +87737,11 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr"/>
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -86945,7 +88029,11 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr"/>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -87233,7 +88321,11 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr"/>
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -87521,7 +88613,11 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr"/>
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -87809,7 +88905,11 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr"/>
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -88097,7 +89197,11 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr"/>
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -88385,7 +89489,11 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -88673,7 +89781,11 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr"/>
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -88961,7 +90073,11 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr"/>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -89249,7 +90365,11 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -89829,7 +90949,11 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr"/>
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -90117,7 +91241,11 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr"/>
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -90405,7 +91533,11 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr"/>
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -90693,7 +91825,11 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr"/>
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -90981,7 +92117,11 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr"/>
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -91269,7 +92409,11 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr"/>
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -91557,7 +92701,11 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr"/>
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -91845,7 +92993,11 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr"/>
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -92133,7 +93285,11 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr"/>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -92421,7 +93577,11 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr"/>
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -93001,7 +94161,11 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr"/>
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -93289,7 +94453,11 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr"/>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -93577,7 +94745,11 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -93865,7 +95037,11 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr"/>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -94153,7 +95329,11 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr"/>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -94441,7 +95621,11 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr"/>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -94729,7 +95913,11 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr"/>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -95017,7 +96205,11 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr"/>
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -95305,7 +96497,11 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -95593,7 +96789,11 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr"/>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -96173,7 +97373,11 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr"/>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -96461,7 +97665,11 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr"/>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -96749,7 +97957,11 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -97037,7 +98249,11 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -97325,7 +98541,11 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr"/>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -97613,7 +98833,11 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr"/>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -97901,7 +99125,11 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr"/>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -98189,7 +99417,11 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr"/>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -98477,7 +99709,11 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -98765,7 +100001,11 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr"/>
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>2025-08-25</t>
